--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -1191,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118383460</v>
+        <v>118383458</v>
       </c>
       <c r="B6" t="n">
-        <v>106569</v>
+        <v>106776</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,50 +1203,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219955</v>
+        <v>220079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427363</v>
+        <v>427247</v>
       </c>
       <c r="R6" t="n">
-        <v>6464208</v>
+        <v>6464047</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1287,7 +1275,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1315,10 +1302,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118383458</v>
+        <v>118383459</v>
       </c>
       <c r="B7" t="n">
-        <v>106776</v>
+        <v>106569</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1327,38 +1314,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>219955</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427247</v>
+        <v>427361</v>
       </c>
       <c r="R7" t="n">
-        <v>6464047</v>
+        <v>6464193</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,6 +1398,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118383461</v>
+        <v>118383462</v>
       </c>
       <c r="B8" t="n">
         <v>106569</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427338</v>
+        <v>427289</v>
       </c>
       <c r="R8" t="n">
-        <v>6464201</v>
+        <v>6464162</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118383462</v>
+        <v>118383461</v>
       </c>
       <c r="B9" t="n">
         <v>106569</v>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427289</v>
+        <v>427338</v>
       </c>
       <c r="R9" t="n">
-        <v>6464162</v>
+        <v>6464201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118383459</v>
+        <v>118383460</v>
       </c>
       <c r="B10" t="n">
         <v>106569</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427361</v>
+        <v>427363</v>
       </c>
       <c r="R10" t="n">
-        <v>6464193</v>
+        <v>6464208</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -1191,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118383458</v>
+        <v>118383462</v>
       </c>
       <c r="B6" t="n">
-        <v>106776</v>
+        <v>106569</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1203,38 +1203,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>219955</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427247</v>
+        <v>427289</v>
       </c>
       <c r="R6" t="n">
-        <v>6464047</v>
+        <v>6464162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,6 +1287,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1291,7 +1304,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1302,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118383459</v>
+        <v>118383461</v>
       </c>
       <c r="B7" t="n">
         <v>106569</v>
@@ -1342,7 +1355,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1354,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427361</v>
+        <v>427338</v>
       </c>
       <c r="R7" t="n">
-        <v>6464193</v>
+        <v>6464201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,7 +1428,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1426,7 +1439,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118383462</v>
+        <v>118383459</v>
       </c>
       <c r="B8" t="n">
         <v>106569</v>
@@ -1461,12 +1474,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1478,10 +1491,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427289</v>
+        <v>427361</v>
       </c>
       <c r="R8" t="n">
-        <v>6464162</v>
+        <v>6464193</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1552,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1550,7 +1563,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118383461</v>
+        <v>118383460</v>
       </c>
       <c r="B9" t="n">
         <v>106569</v>
@@ -1585,12 +1598,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1602,10 +1615,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427338</v>
+        <v>427363</v>
       </c>
       <c r="R9" t="n">
-        <v>6464201</v>
+        <v>6464208</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1663,7 +1676,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1674,10 +1687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118383460</v>
+        <v>118383458</v>
       </c>
       <c r="B10" t="n">
-        <v>106569</v>
+        <v>106776</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,50 +1699,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219955</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427363</v>
+        <v>427247</v>
       </c>
       <c r="R10" t="n">
-        <v>6464208</v>
+        <v>6464047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1770,7 +1771,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -1194,7 +1194,7 @@
         <v>118383462</v>
       </c>
       <c r="B6" t="n">
-        <v>106569</v>
+        <v>106576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118383461</v>
+        <v>118383460</v>
       </c>
       <c r="B7" t="n">
-        <v>106569</v>
+        <v>106576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427338</v>
+        <v>427363</v>
       </c>
       <c r="R7" t="n">
-        <v>6464201</v>
+        <v>6464208</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1439,10 +1439,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118383459</v>
+        <v>118383458</v>
       </c>
       <c r="B8" t="n">
-        <v>106569</v>
+        <v>106783</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,50 +1451,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219955</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427361</v>
+        <v>427247</v>
       </c>
       <c r="R8" t="n">
-        <v>6464193</v>
+        <v>6464047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1535,7 +1523,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1552,7 +1539,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1563,10 +1550,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118383460</v>
+        <v>118383461</v>
       </c>
       <c r="B9" t="n">
-        <v>106569</v>
+        <v>106576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1598,12 +1585,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1615,10 +1602,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427363</v>
+        <v>427338</v>
       </c>
       <c r="R9" t="n">
-        <v>6464208</v>
+        <v>6464201</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1676,7 +1663,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1687,10 +1674,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118383458</v>
+        <v>118383459</v>
       </c>
       <c r="B10" t="n">
-        <v>106776</v>
+        <v>106576</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1699,38 +1686,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220079</v>
+        <v>219955</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427247</v>
+        <v>427361</v>
       </c>
       <c r="R10" t="n">
-        <v>6464047</v>
+        <v>6464193</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1771,6 +1770,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -1191,7 +1191,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118383462</v>
+        <v>118383459</v>
       </c>
       <c r="B6" t="n">
         <v>106576</v>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427289</v>
+        <v>427361</v>
       </c>
       <c r="R6" t="n">
-        <v>6464162</v>
+        <v>6464193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,7 +1315,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118383460</v>
+        <v>118383461</v>
       </c>
       <c r="B7" t="n">
         <v>106576</v>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1367,10 +1367,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427363</v>
+        <v>427338</v>
       </c>
       <c r="R7" t="n">
-        <v>6464208</v>
+        <v>6464201</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118383458</v>
+        <v>118383460</v>
       </c>
       <c r="B8" t="n">
-        <v>106783</v>
+        <v>106576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1451,38 +1451,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>219955</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427247</v>
+        <v>427363</v>
       </c>
       <c r="R8" t="n">
-        <v>6464047</v>
+        <v>6464208</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,6 +1535,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1550,7 +1563,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118383461</v>
+        <v>118383462</v>
       </c>
       <c r="B9" t="n">
         <v>106576</v>
@@ -1585,7 +1598,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1602,10 +1615,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427338</v>
+        <v>427289</v>
       </c>
       <c r="R9" t="n">
-        <v>6464201</v>
+        <v>6464162</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,10 +1687,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118383459</v>
+        <v>118383458</v>
       </c>
       <c r="B10" t="n">
-        <v>106576</v>
+        <v>106783</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,50 +1699,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219955</v>
+        <v>220079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427361</v>
+        <v>427247</v>
       </c>
       <c r="R10" t="n">
-        <v>6464193</v>
+        <v>6464047</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1770,7 +1771,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>70537577</v>
       </c>
       <c r="B4" t="n">
-        <v>105123</v>
+        <v>107442</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427222.3972293444</v>
+        <v>427222</v>
       </c>
       <c r="R4" t="n">
-        <v>6464084.841835432</v>
+        <v>6464085</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,19 +1008,9 @@
           <t>2016-06-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-06-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>70537571</v>
       </c>
       <c r="B2" t="n">
-        <v>98138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,42 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>70537578</v>
+        <v>70537576</v>
       </c>
       <c r="B3" t="n">
-        <v>106961</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220079</v>
+        <v>219955</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>427222</v>
+        <v>427284</v>
       </c>
       <c r="R3" t="n">
-        <v>6464085</v>
+        <v>6464154</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,42 +896,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70537577</v>
+        <v>118383459</v>
       </c>
       <c r="B4" t="n">
-        <v>107040</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220103</v>
+        <v>219955</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klasefibbla</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crepis praemorsa</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Walther</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -949,16 +934,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Frugården, Vg</t>
+          <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>427222</v>
+        <v>427361</v>
       </c>
       <c r="R4" t="n">
-        <v>6464085</v>
+        <v>6464193</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -985,17 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mager naturbetesmark</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,18 +987,24 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Naturlig betesmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1026,15 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89407668</v>
+        <v>118383460</v>
       </c>
       <c r="B5" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,7 +1045,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,16 +1053,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Frugården, Vg</t>
+          <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>427283.684526759</v>
+        <v>427363</v>
       </c>
       <c r="R5" t="n">
-        <v>6464153.603968509</v>
+        <v>6464208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,29 +1090,14 @@
           <t>Rådene</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>OV-Skö-0419</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,18 +1106,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Mager naturbetesmark</t>
+          <t>Naturlig betesmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sofia Lund</t>
+          <t>Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1155,21 +1128,16 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Billingens flora</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118383460</v>
+        <v>118383461</v>
       </c>
       <c r="B6" t="n">
-        <v>106753</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,12 +1164,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1213,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>427363</v>
+        <v>427338</v>
       </c>
       <c r="R6" t="n">
-        <v>6464208</v>
+        <v>6464201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1285,50 +1253,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118383458</v>
+        <v>118383462</v>
       </c>
       <c r="B7" t="n">
-        <v>106961</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>219955</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Slåttergubbe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Arnica montana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>427247</v>
+        <v>427289</v>
       </c>
       <c r="R7" t="n">
-        <v>6464047</v>
+        <v>6464162</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1369,6 +1344,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1396,62 +1372,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118383462</v>
+        <v>70537578</v>
       </c>
       <c r="B8" t="n">
-        <v>106753</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219955</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
+          <t>Frugården, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>427289</v>
+        <v>427222</v>
       </c>
       <c r="R8" t="n">
-        <v>6464162</v>
+        <v>6464085</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,12 +1446,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2016-06-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mager naturbetesmark</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,24 +1465,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Naturlig betesmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1520,62 +1487,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118383461</v>
+        <v>118383458</v>
       </c>
       <c r="B9" t="n">
-        <v>106753</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219955</v>
+        <v>220079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>427338</v>
+        <v>427247</v>
       </c>
       <c r="R9" t="n">
-        <v>6464201</v>
+        <v>6464047</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,7 +1566,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1644,42 +1593,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118383459</v>
+        <v>70537577</v>
       </c>
       <c r="B10" t="n">
-        <v>106753</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>108194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219955</v>
+        <v>220103</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Klasefibbla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Crepis praemorsa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Walther</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1687,19 +1631,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Frugården, Obj. 12 i Äng o Hage 89, Vg</t>
+          <t>Frugården, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>427361</v>
+        <v>427222</v>
       </c>
       <c r="R10" t="n">
-        <v>6464193</v>
+        <v>6464085</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,12 +1667,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
+          <t>2016-06-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mager naturbetesmark</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,24 +1686,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Naturlig betesmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">

--- a/artfynd/A 13517-2024 artfynd.xlsx
+++ b/artfynd/A 13517-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70537571</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70537576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118383459</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118383460</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118383461</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1369,6 +1399,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118383462</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70537578</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118383458</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1705,8 +1750,24 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70537577</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>